--- a/artfynd/A 4192-2025 artfynd.xlsx
+++ b/artfynd/A 4192-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126388328</v>
       </c>
       <c r="B2" t="n">
-        <v>77941</v>
+        <v>77944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126387179</v>
       </c>
       <c r="B3" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126387183</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>126388441</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126387170</v>
       </c>
       <c r="B6" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>126388047</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4192-2025 artfynd.xlsx
+++ b/artfynd/A 4192-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>126388328</v>
       </c>
       <c r="B2" t="n">
-        <v>77944</v>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126387179</v>
+        <v>126388441</v>
       </c>
       <c r="B3" t="n">
-        <v>75075</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjabraviken, Tjabraviken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594368</v>
+        <v>594317</v>
       </c>
       <c r="R3" t="n">
-        <v>7291074</v>
+        <v>7291019</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126387183</v>
+        <v>126388047</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594368</v>
+        <v>594286</v>
       </c>
       <c r="R4" t="n">
-        <v>7291074</v>
+        <v>7291044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126388441</v>
+        <v>126387170</v>
       </c>
       <c r="B5" t="n">
-        <v>91541</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -996,37 +1000,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjabraviken, Tjabraviken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594317</v>
+        <v>594370</v>
       </c>
       <c r="R5" t="n">
-        <v>7291019</v>
+        <v>7291075</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1068,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,32 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126387170</v>
+        <v>126387183</v>
       </c>
       <c r="B6" t="n">
-        <v>82792</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594370</v>
+        <v>594368</v>
       </c>
       <c r="R6" t="n">
-        <v>7291075</v>
+        <v>7291074</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126388047</v>
+        <v>126387179</v>
       </c>
       <c r="B7" t="n">
-        <v>91241</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,21 +1204,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594286</v>
+        <v>594368</v>
       </c>
       <c r="R7" t="n">
-        <v>7291044</v>
+        <v>7291074</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 4192-2025 artfynd.xlsx
+++ b/artfynd/A 4192-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126388328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126388441</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126388047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387170</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387183</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,8 +1322,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387179</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>